--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128254623</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128254623</v>
       </c>
       <c r="B2" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128254623</v>
       </c>
       <c r="B2" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128254623</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,329 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129009415</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fållgölen/Alserum, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>561332</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6453887</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hackspår på trädstam</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129009776</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fållgölen/Alserum, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>561288</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6453935</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska hackspår på trädstam</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129009468</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98636</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fållgölen/Alserum, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>561289</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6453889</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åtvid</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>En växtplats med ett 20-tal bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129009415</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129009776</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129009415</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129009776</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>129009415</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129009776</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34708-2025 artfynd.xlsx
+++ b/artfynd/A 34708-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>129009468</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
